--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -594,6 +594,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>240.4</v>
       </c>
@@ -767,6 +772,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>535.2</v>
       </c>
@@ -932,6 +942,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>80.90000000000001</v>
       </c>
@@ -1089,6 +1104,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>102.2</v>
       </c>
@@ -1243,6 +1263,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>152.1</v>
       </c>
@@ -1393,6 +1418,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>117.3</v>
       </c>
@@ -1540,6 +1570,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>1125.5</v>
       </c>
@@ -1681,6 +1716,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>381.1</v>
       </c>
@@ -1821,6 +1861,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>121.7</v>
       </c>
@@ -1956,6 +2001,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>27.2</v>
       </c>
@@ -2091,6 +2141,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>190.3</v>
       </c>
@@ -2225,6 +2280,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>60.4</v>
       </c>
@@ -2354,6 +2414,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>103.6</v>
       </c>
@@ -2482,6 +2547,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>258.7</v>
       </c>
@@ -2609,6 +2679,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>57.1</v>
       </c>
@@ -2736,6 +2811,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>64.7</v>
       </c>
@@ -2862,6 +2942,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>65.8</v>
       </c>
@@ -2988,6 +3073,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>771.6</v>
       </c>
@@ -3109,6 +3199,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>14</v>
       </c>
@@ -3233,6 +3328,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>170.1</v>
       </c>
@@ -3355,6 +3455,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>534.2</v>
       </c>
@@ -3473,6 +3578,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>78.7</v>
       </c>
@@ -3586,6 +3696,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>143.6</v>
       </c>
@@ -3703,6 +3818,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>93.3</v>
       </c>
@@ -3819,6 +3939,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>56.4</v>
       </c>
@@ -3939,6 +4064,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>72.59999999999999</v>
       </c>
@@ -4058,6 +4188,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>80.59999999999999</v>
       </c>
@@ -4172,6 +4307,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>57.7</v>
       </c>
@@ -4289,6 +4429,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>66.09999999999999</v>
       </c>
@@ -4405,6 +4550,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>63.2</v>
       </c>
@@ -4516,6 +4666,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>166.5</v>
       </c>
@@ -4630,6 +4785,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>105.2</v>
       </c>
@@ -4740,6 +4900,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>356.4</v>
       </c>
@@ -4850,6 +5015,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>186</v>
       </c>
@@ -4958,6 +5128,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>58.4</v>
       </c>
@@ -5068,6 +5243,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>29.2</v>
       </c>
@@ -5170,6 +5350,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>113.3</v>
       </c>
@@ -5276,6 +5461,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>110.6</v>
       </c>
@@ -5378,6 +5568,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>117.8</v>
       </c>
@@ -5478,6 +5673,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>187.8</v>
       </c>
@@ -5578,6 +5778,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>27.1</v>
       </c>
@@ -5678,6 +5883,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>62.7</v>
       </c>
@@ -5782,6 +5992,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>25.5</v>
       </c>
@@ -5881,6 +6096,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>143.1</v>
       </c>
@@ -5975,6 +6195,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>55</v>
       </c>
@@ -6069,6 +6294,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>174.7</v>
       </c>
@@ -6161,6 +6391,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>129.9</v>
       </c>
@@ -6252,6 +6487,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>48.6</v>
       </c>
@@ -6343,6 +6583,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>112.2</v>
       </c>
@@ -6433,6 +6678,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>299.4</v>
       </c>
@@ -6527,6 +6777,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>115.9</v>
       </c>
@@ -6617,6 +6872,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>18.7</v>
       </c>
@@ -6707,6 +6967,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>68.3</v>
       </c>
@@ -6796,6 +7061,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>18.1</v>
       </c>
@@ -6883,6 +7153,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -6946,6 +7221,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>76.5</v>
       </c>
@@ -7007,6 +7287,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>96.8</v>
       </c>
@@ -7068,6 +7353,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>26.8</v>
       </c>
@@ -7129,6 +7419,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>29.8</v>
       </c>
@@ -7190,6 +7485,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>20.4</v>
       </c>
@@ -7251,6 +7551,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>20.8</v>
       </c>
@@ -7312,6 +7617,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>42</v>
       </c>
@@ -7373,6 +7683,11 @@
           <t>Bjurholm</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>13.4</v>
       </c>
@@ -7432,6 +7747,11 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I65" t="n">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6476,10 +6476,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -1870,7 +1870,7 @@
         <v>121.7</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
         <v>11</v>
@@ -1897,10 +1897,10 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1942,6 +1942,7 @@
 Järpe
 Spillkråka
 Tjäder
+Tofsmes
 Fläcknycklar</t>
         </is>
       </c>
@@ -4168,7 +4169,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Björnberget NV</t>
+          <t>Björnberget SV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4194,19 +4195,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>80.59999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4221,15 +4222,138 @@
         <v>15</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
         <v>22</v>
       </c>
       <c r="T28" t="n">
+        <v>32</v>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Liten aspgelélav
+Skrovlig taggsvamp
+Tornseglare
+Dropptaggsvamp
+Dvärgbägarlav
+Gammelgransskål
+Göktyta
+Lunglav
+Mörk kolflarnlav
+Nordtagging
+Orange taggsvamp
+Reliktbock
+Älg
+Barkticka
+Bårdlav
+Skinnlav
+Stor aspticka
+Stuplav
+Kungsfågel
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="V28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Björnberget SV artfynd.xlsx", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Björnberget SV karta.png", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Björnberget SV karta knärot.png", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget SV FSC-klagomål.docx", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget SV FSC-klagomål mail.docx", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget SV tillsynsbegäran.docx", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget SV tillsynsbegäran mail.docx", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget SV prioriterade fågelarter.docx", "Björnberget SV")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Björnberget NV</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>13</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>15</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>22</v>
+      </c>
+      <c r="T29" t="n">
         <v>55</v>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skrovlig taggsvamp
@@ -4255,161 +4379,39 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V28">
+      <c r="V29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Björnberget NV artfynd.xlsx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Björnberget NV karta.png", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget NV FSC-klagomål.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="Z28">
+      <c r="Z29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget NV FSC-klagomål mail.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget NV tillsynsbegäran.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget NV tillsynsbegäran mail.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget NV prioriterade fågelarter.docx", "Björnberget NV")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Björnberget SV</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>10</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>14</v>
-      </c>
-      <c r="R29" t="n">
-        <v>4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>21</v>
-      </c>
-      <c r="T29" t="n">
-        <v>31</v>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Liten aspgelélav
-Skrovlig taggsvamp
-Dropptaggsvamp
-Dvärgbägarlav
-Gammelgransskål
-Göktyta
-Lunglav
-Mörk kolflarnlav
-Nordtagging
-Orange taggsvamp
-Reliktbock
-Älg
-Barkticka
-Bårdlav
-Skinnlav
-Stor aspticka
-Stuplav
-Kungsfågel
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="V29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Björnberget SV artfynd.xlsx", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Björnberget SV karta.png", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Björnberget SV karta knärot.png", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget SV FSC-klagomål.docx", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget SV FSC-klagomål mail.docx", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget SV tillsynsbegäran.docx", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget SV tillsynsbegäran mail.docx", "Björnberget SV")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget SV prioriterade fågelarter.docx", "Björnberget SV")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Johannesbomyran</t>
+          <t>Kläpptjärnen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4431,46 +4433,164 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>66.09999999999999</v>
+        <v>113.3</v>
       </c>
       <c r="J30" t="n">
         <v>4</v>
       </c>
       <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>18</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>21</v>
+      </c>
+      <c r="T30" t="n">
+        <v>45</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Goliatmusseron
+Jättemusseron
+Skrovlig taggsvamp
+Blå taggsvamp
+Dropptaggsvamp
+Dvärgbägarlav
+Kolflarnlav
+Motaggsvamp
+Mörk kolflarnlav
+Orange taggsvamp
+Skarp dropptaggsvamp
+Tallfingersvamp
+Talltaggsvamp
+Tallticka
+Tretåig hackspett
+Vaddporing
+Vedflamlav
+Vedskivlav
+Plattlummer
+Gröngöling
+Revlummer</t>
+        </is>
+      </c>
+      <c r="V30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Kläpptjärnen artfynd.xlsx", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Kläpptjärnen karta.png", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Kläpptjärnen FSC-klagomål.docx", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Kläpptjärnen FSC-klagomål mail.docx", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Kläpptjärnen tillsynsbegäran.docx", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Kläpptjärnen tillsynsbegäran mail.docx", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kläpptjärnen prioriterade fågelarter.docx", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Johannesbomyran</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
         <v>7</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L31" t="n">
         <v>10</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>12</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>20</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>132</v>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -4494,104 +4614,104 @@
 Ljungpipare</t>
         </is>
       </c>
-      <c r="V30">
+      <c r="V31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Johannesbomyran artfynd.xlsx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Johannesbomyran karta.png", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Johannesbomyran karta knärot.png", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Johannesbomyran FSC-klagomål.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="Z30">
+      <c r="Z31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Johannesbomyran FSC-klagomål mail.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Johannesbomyran tillsynsbegäran.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Johannesbomyran tillsynsbegäran mail.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Johannesbomyran prioriterade fågelarter.docx", "Johannesbomyran")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Stockbäcken</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="D32" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>63.2</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>12</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>4</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>16</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>4</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>19</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>72</v>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>Aspgelélav
 Garnlav
@@ -4614,100 +4734,100 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V31">
+      <c r="V32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Stockbäcken artfynd.xlsx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Stockbäcken karta.png", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Stockbäcken FSC-klagomål.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="Z31">
+      <c r="Z32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Stockbäcken FSC-klagomål mail.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Stockbäcken tillsynsbegäran.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stockbäcken tillsynsbegäran mail.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Stockbäcken prioriterade fågelarter.docx", "Stockbäcken")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Lögdaselet</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="D33" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>166.5</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>5</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L33" t="n">
         <v>10</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M33" t="n">
         <v>2</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>12</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>2</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>18</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>48</v>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -4729,104 +4849,104 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="V32">
+      <c r="V33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Lögdaselet artfynd.xlsx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lögdaselet karta.png", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Lögdaselet karta knärot.png", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lögdaselet FSC-klagomål.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="Z32">
+      <c r="Z33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lögdaselet FSC-klagomål mail.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lögdaselet tillsynsbegäran.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lögdaselet tillsynsbegäran mail.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lögdaselet prioriterade fågelarter.docx", "Lögdaselet")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Holmtjärnen</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="D34" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>105.2</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>11</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>6</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>17</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>6</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>18</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>39</v>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -4848,100 +4968,100 @@
 Bårdlav</t>
         </is>
       </c>
-      <c r="V33">
+      <c r="V34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Holmtjärnen artfynd.xlsx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Holmtjärnen karta.png", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Holmtjärnen FSC-klagomål.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="Z33">
+      <c r="Z34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Holmtjärnen FSC-klagomål mail.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Holmtjärnen tillsynsbegäran.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Holmtjärnen tillsynsbegäran mail.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Holmtjärnen prioriterade fågelarter.docx", "Holmtjärnen")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Aspmyrbäcken</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+      <c r="D35" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>356.4</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>5</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>9</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>3</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>12</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>3</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S35" t="n">
         <v>18</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>72</v>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lappticka
@@ -4963,100 +5083,100 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="V34">
+      <c r="V35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Aspmyrbäcken artfynd.xlsx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Aspmyrbäcken karta.png", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Aspmyrbäcken FSC-klagomål.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="Z34">
+      <c r="Z35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Aspmyrbäcken FSC-klagomål mail.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Aspmyrbäcken tillsynsbegäran.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Aspmyrbäcken tillsynsbegäran mail.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Aspmyrbäcken prioriterade fågelarter.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Gubbmyran</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+      <c r="D36" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I36" t="n">
         <v>186</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>9</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M36" t="n">
         <v>5</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>14</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>5</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S36" t="n">
         <v>16</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>34</v>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -5076,100 +5196,100 @@
 Trådticka</t>
         </is>
       </c>
-      <c r="V35">
+      <c r="V36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Gubbmyran artfynd.xlsx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Gubbmyran karta.png", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Gubbmyran FSC-klagomål.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="Z35">
+      <c r="Z36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Gubbmyran FSC-klagomål mail.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Gubbmyran tillsynsbegäran.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gubbmyran tillsynsbegäran mail.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Gubbmyran prioriterade fågelarter.docx", "Gubbmyran")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Kälkåsen</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="D37" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>58.4</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>7</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>4</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>11</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>4</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S37" t="n">
         <v>14</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>32</v>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -5187,104 +5307,104 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V36">
+      <c r="V37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Kälkåsen artfynd.xlsx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Kälkåsen karta.png", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Kälkåsen karta knärot.png", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Kälkåsen FSC-klagomål.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="Z36">
+      <c r="Z37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Kälkåsen FSC-klagomål mail.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Kälkåsen tillsynsbegäran.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Kälkåsen tillsynsbegäran mail.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kälkåsen prioriterade fågelarter.docx", "Kälkåsen")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Björnberget N</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D37" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="D38" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Bjurholm</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I38" t="n">
         <v>29.2</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>3</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L38" t="n">
         <v>8</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>3</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>11</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>3</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>14</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>22</v>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gräddporing
@@ -5302,139 +5422,28 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V37">
+      <c r="V38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Björnberget N artfynd.xlsx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Björnberget N karta.png", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget N FSC-klagomål.docx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="Z37">
+      <c r="Z38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget N FSC-klagomål mail.docx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget N tillsynsbegäran.docx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget N tillsynsbegäran mail.docx", "Björnberget N")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Kläpptjärnen</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>11</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>14</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>14</v>
-      </c>
-      <c r="T38" t="n">
-        <v>33</v>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>Goliatmusseron
-Jättemusseron
-Skrovlig taggsvamp
-Blå taggsvamp
-Dropptaggsvamp
-Dvärgbägarlav
-Motaggsvamp
-Orange taggsvamp
-Skarp dropptaggsvamp
-Tallfingersvamp
-Talltaggsvamp
-Tallticka
-Tretåig hackspett
-Vaddporing</t>
-        </is>
-      </c>
-      <c r="V38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/artfynd/Kläpptjärnen artfynd.xlsx", "Kläpptjärnen")</f>
-        <v/>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Kläpptjärnen karta.png", "Kläpptjärnen")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Kläpptjärnen FSC-klagomål.docx", "Kläpptjärnen")</f>
-        <v/>
-      </c>
-      <c r="Z38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Kläpptjärnen FSC-klagomål mail.docx", "Kläpptjärnen")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Kläpptjärnen tillsynsbegäran.docx", "Kläpptjärnen")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Kläpptjärnen tillsynsbegäran mail.docx", "Kläpptjärnen")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kläpptjärnen prioriterade fågelarter.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AD65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -542,30 +542,35 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Geotifflänk</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -725,26 +730,30 @@
         <v/>
       </c>
       <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Råtjärnberget georefererad karta.tif", "Råtjärnberget")</f>
+        <v/>
+      </c>
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Råtjärnberget karta knärot.png", "Råtjärnberget")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Råtjärnberget FSC-klagomål.docx", "Råtjärnberget")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Råtjärnberget FSC-klagomål mail.docx", "Råtjärnberget")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Råtjärnberget tillsynsbegäran.docx", "Råtjärnberget")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Råtjärnberget tillsynsbegäran mail.docx", "Råtjärnberget")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Råtjärnberget prioriterade fågelarter.docx", "Råtjärnberget")</f>
         <v/>
       </c>
@@ -895,26 +904,30 @@
         <v/>
       </c>
       <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Kravattensliden georefererad karta.tif", "Kravattensliden")</f>
+        <v/>
+      </c>
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Kravattensliden karta knärot.png", "Kravattensliden")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Kravattensliden FSC-klagomål.docx", "Kravattensliden")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Kravattensliden FSC-klagomål mail.docx", "Kravattensliden")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Kravattensliden tillsynsbegäran.docx", "Kravattensliden")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Kravattensliden tillsynsbegäran mail.docx", "Kravattensliden")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kravattensliden prioriterade fågelarter.docx", "Kravattensliden")</f>
         <v/>
       </c>
@@ -1057,26 +1070,30 @@
         <v/>
       </c>
       <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Röjdtjärnliden georefererad karta.tif", "Röjdtjärnliden")</f>
+        <v/>
+      </c>
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Röjdtjärnliden karta knärot.png", "Röjdtjärnliden")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Röjdtjärnliden FSC-klagomål.docx", "Röjdtjärnliden")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Röjdtjärnliden FSC-klagomål mail.docx", "Röjdtjärnliden")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Röjdtjärnliden tillsynsbegäran.docx", "Röjdtjärnliden")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Röjdtjärnliden tillsynsbegäran mail.docx", "Röjdtjärnliden")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Röjdtjärnliden prioriterade fågelarter.docx", "Röjdtjärnliden")</f>
         <v/>
       </c>
@@ -1216,26 +1233,30 @@
         <v/>
       </c>
       <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lillgoberget georefererad karta.tif", "Lillgoberget")</f>
+        <v/>
+      </c>
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Lillgoberget karta knärot.png", "Lillgoberget")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lillgoberget FSC-klagomål.docx", "Lillgoberget")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lillgoberget FSC-klagomål mail.docx", "Lillgoberget")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lillgoberget tillsynsbegäran.docx", "Lillgoberget")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lillgoberget tillsynsbegäran mail.docx", "Lillgoberget")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lillgoberget prioriterade fågelarter.docx", "Lillgoberget")</f>
         <v/>
       </c>
@@ -1371,26 +1392,30 @@
         <v/>
       </c>
       <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Baksjökullen georefererad karta.tif", "Baksjökullen")</f>
+        <v/>
+      </c>
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Baksjökullen karta knärot.png", "Baksjökullen")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Baksjökullen FSC-klagomål.docx", "Baksjökullen")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Baksjökullen FSC-klagomål mail.docx", "Baksjökullen")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Baksjökullen tillsynsbegäran.docx", "Baksjökullen")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Baksjökullen tillsynsbegäran mail.docx", "Baksjökullen")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Baksjökullen prioriterade fågelarter.docx", "Baksjökullen")</f>
         <v/>
       </c>
@@ -1523,26 +1548,30 @@
         <v/>
       </c>
       <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Fulberget georefererad karta.tif", "Fulberget")</f>
+        <v/>
+      </c>
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Fulberget karta knärot.png", "Fulberget")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Fulberget FSC-klagomål.docx", "Fulberget")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Fulberget FSC-klagomål mail.docx", "Fulberget")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Fulberget tillsynsbegäran.docx", "Fulberget")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Fulberget tillsynsbegäran mail.docx", "Fulberget")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Fulberget prioriterade fågelarter.docx", "Fulberget")</f>
         <v/>
       </c>
@@ -1672,23 +1701,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Arnträskbergen karta.png", "Arnträskbergen")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Arnträskbergen georefererad karta.tif", "Arnträskbergen")</f>
+        <v/>
+      </c>
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Arnträskbergen FSC-klagomål.docx", "Arnträskbergen")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Arnträskbergen FSC-klagomål mail.docx", "Arnträskbergen")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Arnträskbergen tillsynsbegäran.docx", "Arnträskbergen")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Arnträskbergen tillsynsbegäran mail.docx", "Arnträskbergen")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Arnträskbergen prioriterade fågelarter.docx", "Arnträskbergen")</f>
         <v/>
       </c>
@@ -1817,23 +1850,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Sundsjölandet karta.png", "Sundsjölandet")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Sundsjölandet georefererad karta.tif", "Sundsjölandet")</f>
+        <v/>
+      </c>
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Sundsjölandet FSC-klagomål.docx", "Sundsjölandet")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Sundsjölandet FSC-klagomål mail.docx", "Sundsjölandet")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Sundsjölandet tillsynsbegäran.docx", "Sundsjölandet")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Sundsjölandet tillsynsbegäran mail.docx", "Sundsjölandet")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Sundsjölandet prioriterade fågelarter.docx", "Sundsjölandet")</f>
         <v/>
       </c>
@@ -1955,26 +1992,30 @@
         <v/>
       </c>
       <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Rislidtjärnarna georefererad karta.tif", "Rislidtjärnarna")</f>
+        <v/>
+      </c>
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Rislidtjärnarna karta knärot.png", "Rislidtjärnarna")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Rislidtjärnarna FSC-klagomål.docx", "Rislidtjärnarna")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Rislidtjärnarna FSC-klagomål mail.docx", "Rislidtjärnarna")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Rislidtjärnarna tillsynsbegäran.docx", "Rislidtjärnarna")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Rislidtjärnarna tillsynsbegäran mail.docx", "Rislidtjärnarna")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Rislidtjärnarna prioriterade fågelarter.docx", "Rislidtjärnarna")</f>
         <v/>
       </c>
@@ -2095,26 +2136,30 @@
         <v/>
       </c>
       <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lill-Lögdåberget O georefererad karta.tif", "Lill-Lögdåberget O")</f>
+        <v/>
+      </c>
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Lill-Lögdåberget O karta knärot.png", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lill-Lögdåberget O FSC-klagomål.docx", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lill-Lögdåberget O FSC-klagomål mail.docx", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lill-Lögdåberget O tillsynsbegäran.docx", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lill-Lögdåberget O tillsynsbegäran mail.docx", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lill-Lögdåberget O prioriterade fågelarter.docx", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
@@ -2234,26 +2279,30 @@
         <v/>
       </c>
       <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Tällvattsåsen georefererad karta.tif", "Tällvattsåsen")</f>
+        <v/>
+      </c>
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Tällvattsåsen karta knärot.png", "Tällvattsåsen")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Tällvattsåsen FSC-klagomål.docx", "Tällvattsåsen")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Tällvattsåsen FSC-klagomål mail.docx", "Tällvattsåsen")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Tällvattsåsen tillsynsbegäran.docx", "Tällvattsåsen")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tällvattsåsen tillsynsbegäran mail.docx", "Tällvattsåsen")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Tällvattsåsen prioriterade fågelarter.docx", "Tällvattsåsen")</f>
         <v/>
       </c>
@@ -2371,23 +2420,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lappberget karta.png", "Lappberget")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lappberget georefererad karta.tif", "Lappberget")</f>
+        <v/>
+      </c>
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lappberget FSC-klagomål.docx", "Lappberget")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lappberget FSC-klagomål mail.docx", "Lappberget")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lappberget tillsynsbegäran.docx", "Lappberget")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lappberget tillsynsbegäran mail.docx", "Lappberget")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lappberget prioriterade fågelarter.docx", "Lappberget")</f>
         <v/>
       </c>
@@ -2505,22 +2558,26 @@
         <v/>
       </c>
       <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Tyfallsjön georefererad karta.tif", "Tyfallsjön")</f>
+        <v/>
+      </c>
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Tyfallsjön karta knärot.png", "Tyfallsjön")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Tyfallsjön FSC-klagomål.docx", "Tyfallsjön")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Tyfallsjön FSC-klagomål mail.docx", "Tyfallsjön")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Tyfallsjön tillsynsbegäran.docx", "Tyfallsjön")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tyfallsjön tillsynsbegäran mail.docx", "Tyfallsjön")</f>
         <v/>
       </c>
@@ -2636,23 +2693,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Oxliden karta.png", "Oxliden")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Oxliden georefererad karta.tif", "Oxliden")</f>
+        <v/>
+      </c>
+      <c r="Z15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Oxliden FSC-klagomål.docx", "Oxliden")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Oxliden FSC-klagomål mail.docx", "Oxliden")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Oxliden tillsynsbegäran.docx", "Oxliden")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Oxliden tillsynsbegäran mail.docx", "Oxliden")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Oxliden prioriterade fågelarter.docx", "Oxliden")</f>
         <v/>
       </c>
@@ -2765,26 +2826,30 @@
         <v/>
       </c>
       <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Gålgoberget georefererad karta.tif", "Gålgoberget")</f>
+        <v/>
+      </c>
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Gålgoberget karta knärot.png", "Gålgoberget")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Gålgoberget FSC-klagomål.docx", "Gålgoberget")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Gålgoberget FSC-klagomål mail.docx", "Gålgoberget")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Gålgoberget tillsynsbegäran.docx", "Gålgoberget")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gålgoberget tillsynsbegäran mail.docx", "Gålgoberget")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Gålgoberget prioriterade fågelarter.docx", "Gålgoberget")</f>
         <v/>
       </c>
@@ -2896,26 +2961,30 @@
         <v/>
       </c>
       <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Orratjärnskullen georefererad karta.tif", "Orratjärnskullen")</f>
+        <v/>
+      </c>
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Orratjärnskullen karta knärot.png", "Orratjärnskullen")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Orratjärnskullen FSC-klagomål.docx", "Orratjärnskullen")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Orratjärnskullen FSC-klagomål mail.docx", "Orratjärnskullen")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Orratjärnskullen tillsynsbegäran.docx", "Orratjärnskullen")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Orratjärnskullen tillsynsbegäran mail.docx", "Orratjärnskullen")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Orratjärnskullen prioriterade fågelarter.docx", "Orratjärnskullen")</f>
         <v/>
       </c>
@@ -3027,26 +3096,30 @@
         <v/>
       </c>
       <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Hötjärnberget georefererad karta.tif", "Hötjärnberget")</f>
+        <v/>
+      </c>
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Hötjärnberget karta knärot.png", "Hötjärnberget")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Hötjärnberget FSC-klagomål.docx", "Hötjärnberget")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Hötjärnberget FSC-klagomål mail.docx", "Hötjärnberget")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Hötjärnberget tillsynsbegäran.docx", "Hötjärnberget")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Hötjärnberget tillsynsbegäran mail.docx", "Hötjärnberget")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Hötjärnberget prioriterade fågelarter.docx", "Hötjärnberget")</f>
         <v/>
       </c>
@@ -3156,23 +3229,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Glesskallberget karta.png", "Glesskallberget")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Glesskallberget georefererad karta.tif", "Glesskallberget")</f>
+        <v/>
+      </c>
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Glesskallberget FSC-klagomål.docx", "Glesskallberget")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Glesskallberget FSC-klagomål mail.docx", "Glesskallberget")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Glesskallberget tillsynsbegäran.docx", "Glesskallberget")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Glesskallberget tillsynsbegäran mail.docx", "Glesskallberget")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Glesskallberget prioriterade fågelarter.docx", "Glesskallberget")</f>
         <v/>
       </c>
@@ -3282,26 +3359,30 @@
         <v/>
       </c>
       <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Stormyrbäcken georefererad karta.tif", "Stormyrbäcken")</f>
+        <v/>
+      </c>
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Stormyrbäcken karta knärot.png", "Stormyrbäcken")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Stormyrbäcken FSC-klagomål.docx", "Stormyrbäcken")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Stormyrbäcken FSC-klagomål mail.docx", "Stormyrbäcken")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Stormyrbäcken tillsynsbegäran.docx", "Stormyrbäcken")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stormyrbäcken tillsynsbegäran mail.docx", "Stormyrbäcken")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Stormyrbäcken prioriterade fågelarter.docx", "Stormyrbäcken")</f>
         <v/>
       </c>
@@ -3409,26 +3490,30 @@
         <v/>
       </c>
       <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Bastuberget georefererad karta.tif", "Bastuberget")</f>
+        <v/>
+      </c>
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Bastuberget karta knärot.png", "Bastuberget")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Bastuberget FSC-klagomål.docx", "Bastuberget")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Bastuberget FSC-klagomål mail.docx", "Bastuberget")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Bastuberget tillsynsbegäran.docx", "Bastuberget")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Bastuberget tillsynsbegäran mail.docx", "Bastuberget")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Bastuberget prioriterade fågelarter.docx", "Bastuberget")</f>
         <v/>
       </c>
@@ -3535,23 +3620,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lögdeälven käringberget karta.png", "Lögdeälven käringberget")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lögdeälven käringberget georefererad karta.tif", "Lögdeälven käringberget")</f>
+        <v/>
+      </c>
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lögdeälven käringberget FSC-klagomål.docx", "Lögdeälven käringberget")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lögdeälven käringberget FSC-klagomål mail.docx", "Lögdeälven käringberget")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lögdeälven käringberget tillsynsbegäran.docx", "Lögdeälven käringberget")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lögdeälven käringberget tillsynsbegäran mail.docx", "Lögdeälven käringberget")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lögdeälven käringberget prioriterade fågelarter.docx", "Lögdeälven käringberget")</f>
         <v/>
       </c>
@@ -3657,19 +3746,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Gåsselmyran karta.png", "Gåsselmyran")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Gåsselmyran georefererad karta.tif", "Gåsselmyran")</f>
+        <v/>
+      </c>
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Gåsselmyran FSC-klagomål.docx", "Gåsselmyran")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Gåsselmyran FSC-klagomål mail.docx", "Gåsselmyran")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Gåsselmyran tillsynsbegäran.docx", "Gåsselmyran")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gåsselmyran tillsynsbegäran mail.docx", "Gåsselmyran")</f>
         <v/>
       </c>
@@ -3775,23 +3868,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Käringberget SV karta.png", "Käringberget SV")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Käringberget SV georefererad karta.tif", "Käringberget SV")</f>
+        <v/>
+      </c>
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Käringberget SV FSC-klagomål.docx", "Käringberget SV")</f>
         <v/>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Käringberget SV FSC-klagomål mail.docx", "Käringberget SV")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Käringberget SV tillsynsbegäran.docx", "Käringberget SV")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Käringberget SV tillsynsbegäran mail.docx", "Käringberget SV")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Käringberget SV prioriterade fågelarter.docx", "Käringberget SV")</f>
         <v/>
       </c>
@@ -3896,23 +3993,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Vitstensberget karta.png", "Vitstensberget")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Vitstensberget georefererad karta.tif", "Vitstensberget")</f>
+        <v/>
+      </c>
+      <c r="Z25">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Vitstensberget FSC-klagomål.docx", "Vitstensberget")</f>
         <v/>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Vitstensberget FSC-klagomål mail.docx", "Vitstensberget")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Vitstensberget tillsynsbegäran.docx", "Vitstensberget")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Vitstensberget tillsynsbegäran mail.docx", "Vitstensberget")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Vitstensberget prioriterade fågelarter.docx", "Vitstensberget")</f>
         <v/>
       </c>
@@ -4018,26 +4119,30 @@
         <v/>
       </c>
       <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Karlstjärnberget georefererad karta.tif", "Karlstjärnberget")</f>
+        <v/>
+      </c>
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Karlstjärnberget karta knärot.png", "Karlstjärnberget")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Z26">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Karlstjärnberget FSC-klagomål.docx", "Karlstjärnberget")</f>
         <v/>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Karlstjärnberget FSC-klagomål mail.docx", "Karlstjärnberget")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Karlstjärnberget tillsynsbegäran.docx", "Karlstjärnberget")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Karlstjärnberget tillsynsbegäran mail.docx", "Karlstjärnberget")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Karlstjärnberget prioriterade fågelarter.docx", "Karlstjärnberget")</f>
         <v/>
       </c>
@@ -4142,26 +4247,30 @@
         <v/>
       </c>
       <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Herrbergsliden norr georefererad karta.tif", "Herrbergsliden norr")</f>
+        <v/>
+      </c>
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Herrbergsliden norr karta knärot.png", "Herrbergsliden norr")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Z27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Herrbergsliden norr FSC-klagomål.docx", "Herrbergsliden norr")</f>
         <v/>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Herrbergsliden norr FSC-klagomål mail.docx", "Herrbergsliden norr")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Herrbergsliden norr tillsynsbegäran.docx", "Herrbergsliden norr")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Herrbergsliden norr tillsynsbegäran mail.docx", "Herrbergsliden norr")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Herrbergsliden norr prioriterade fågelarter.docx", "Herrbergsliden norr")</f>
         <v/>
       </c>
@@ -4265,26 +4374,30 @@
         <v/>
       </c>
       <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Björnberget SV georefererad karta.tif", "Björnberget SV")</f>
+        <v/>
+      </c>
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Björnberget SV karta knärot.png", "Björnberget SV")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Z28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget SV FSC-klagomål.docx", "Björnberget SV")</f>
         <v/>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget SV FSC-klagomål mail.docx", "Björnberget SV")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget SV tillsynsbegäran.docx", "Björnberget SV")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget SV tillsynsbegäran mail.docx", "Björnberget SV")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget SV prioriterade fågelarter.docx", "Björnberget SV")</f>
         <v/>
       </c>
@@ -4387,23 +4500,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Björnberget NV karta.png", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Björnberget NV georefererad karta.tif", "Björnberget NV")</f>
+        <v/>
+      </c>
+      <c r="Z29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget NV FSC-klagomål.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget NV FSC-klagomål mail.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget NV tillsynsbegäran.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget NV tillsynsbegäran mail.docx", "Björnberget NV")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget NV prioriterade fågelarter.docx", "Björnberget NV")</f>
         <v/>
       </c>
@@ -4505,23 +4622,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Kläpptjärnen karta.png", "Kläpptjärnen")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Kläpptjärnen georefererad karta.tif", "Kläpptjärnen")</f>
+        <v/>
+      </c>
+      <c r="Z30">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Kläpptjärnen FSC-klagomål.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
-      <c r="Z30">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Kläpptjärnen FSC-klagomål mail.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Kläpptjärnen tillsynsbegäran.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Kläpptjärnen tillsynsbegäran mail.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kläpptjärnen prioriterade fågelarter.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
@@ -4623,26 +4744,30 @@
         <v/>
       </c>
       <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Johannesbomyran georefererad karta.tif", "Johannesbomyran")</f>
+        <v/>
+      </c>
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Johannesbomyran karta knärot.png", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Z31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Johannesbomyran FSC-klagomål.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Johannesbomyran FSC-klagomål mail.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Johannesbomyran tillsynsbegäran.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Johannesbomyran tillsynsbegäran mail.docx", "Johannesbomyran")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Johannesbomyran prioriterade fågelarter.docx", "Johannesbomyran")</f>
         <v/>
       </c>
@@ -4742,23 +4867,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Stockbäcken karta.png", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Stockbäcken georefererad karta.tif", "Stockbäcken")</f>
+        <v/>
+      </c>
+      <c r="Z32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Stockbäcken FSC-klagomål.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Stockbäcken FSC-klagomål mail.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Stockbäcken tillsynsbegäran.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stockbäcken tillsynsbegäran mail.docx", "Stockbäcken")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Stockbäcken prioriterade fågelarter.docx", "Stockbäcken")</f>
         <v/>
       </c>
@@ -4858,26 +4987,30 @@
         <v/>
       </c>
       <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lögdaselet georefererad karta.tif", "Lögdaselet")</f>
+        <v/>
+      </c>
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Lögdaselet karta knärot.png", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Z33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lögdaselet FSC-klagomål.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lögdaselet FSC-klagomål mail.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lögdaselet tillsynsbegäran.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lögdaselet tillsynsbegäran mail.docx", "Lögdaselet")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lögdaselet prioriterade fågelarter.docx", "Lögdaselet")</f>
         <v/>
       </c>
@@ -4976,23 +5109,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Holmtjärnen karta.png", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Holmtjärnen georefererad karta.tif", "Holmtjärnen")</f>
+        <v/>
+      </c>
+      <c r="Z34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Holmtjärnen FSC-klagomål.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Holmtjärnen FSC-klagomål mail.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Holmtjärnen tillsynsbegäran.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Holmtjärnen tillsynsbegäran mail.docx", "Holmtjärnen")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Holmtjärnen prioriterade fågelarter.docx", "Holmtjärnen")</f>
         <v/>
       </c>
@@ -5091,23 +5228,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Aspmyrbäcken karta.png", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Aspmyrbäcken georefererad karta.tif", "Aspmyrbäcken")</f>
+        <v/>
+      </c>
+      <c r="Z35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Aspmyrbäcken FSC-klagomål.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Aspmyrbäcken FSC-klagomål mail.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Aspmyrbäcken tillsynsbegäran.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Aspmyrbäcken tillsynsbegäran mail.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Aspmyrbäcken prioriterade fågelarter.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
@@ -5204,23 +5345,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Gubbmyran karta.png", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Gubbmyran georefererad karta.tif", "Gubbmyran")</f>
+        <v/>
+      </c>
+      <c r="Z36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Gubbmyran FSC-klagomål.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Gubbmyran FSC-klagomål mail.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Gubbmyran tillsynsbegäran.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gubbmyran tillsynsbegäran mail.docx", "Gubbmyran")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Gubbmyran prioriterade fågelarter.docx", "Gubbmyran")</f>
         <v/>
       </c>
@@ -5316,26 +5461,30 @@
         <v/>
       </c>
       <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Kälkåsen georefererad karta.tif", "Kälkåsen")</f>
+        <v/>
+      </c>
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Kälkåsen karta knärot.png", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Z37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Kälkåsen FSC-klagomål.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Kälkåsen FSC-klagomål mail.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Kälkåsen tillsynsbegäran.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Kälkåsen tillsynsbegäran mail.docx", "Kälkåsen")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kälkåsen prioriterade fågelarter.docx", "Kälkåsen")</f>
         <v/>
       </c>
@@ -5430,19 +5579,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Björnberget N karta.png", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Björnberget N georefererad karta.tif", "Björnberget N")</f>
+        <v/>
+      </c>
+      <c r="Z38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Björnberget N FSC-klagomål.docx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Björnberget N FSC-klagomål mail.docx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Björnberget N tillsynsbegäran.docx", "Björnberget N")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget N tillsynsbegäran mail.docx", "Björnberget N")</f>
         <v/>
       </c>
@@ -5537,19 +5690,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Trollberget karta.png", "Trollberget")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Trollberget georefererad karta.tif", "Trollberget")</f>
+        <v/>
+      </c>
+      <c r="Z39">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Trollberget FSC-klagomål.docx", "Trollberget")</f>
         <v/>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Trollberget FSC-klagomål mail.docx", "Trollberget")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Trollberget tillsynsbegäran.docx", "Trollberget")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Trollberget tillsynsbegäran mail.docx", "Trollberget")</f>
         <v/>
       </c>
@@ -5642,19 +5799,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Stensjöåsen karta.png", "Stensjöåsen")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="X40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Stensjöåsen georefererad karta.tif", "Stensjöåsen")</f>
+        <v/>
+      </c>
+      <c r="Z40">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Stensjöåsen FSC-klagomål.docx", "Stensjöåsen")</f>
         <v/>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Stensjöåsen FSC-klagomål mail.docx", "Stensjöåsen")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Stensjöåsen tillsynsbegäran.docx", "Stensjöåsen")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stensjöåsen tillsynsbegäran mail.docx", "Stensjöåsen")</f>
         <v/>
       </c>
@@ -5747,19 +5908,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Stor-Svartliden karta.png", "Stor-Svartliden")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Stor-Svartliden georefererad karta.tif", "Stor-Svartliden")</f>
+        <v/>
+      </c>
+      <c r="Z41">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Stor-Svartliden FSC-klagomål.docx", "Stor-Svartliden")</f>
         <v/>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Stor-Svartliden FSC-klagomål mail.docx", "Stor-Svartliden")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Stor-Svartliden tillsynsbegäran.docx", "Stor-Svartliden")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stor-Svartliden tillsynsbegäran mail.docx", "Stor-Svartliden")</f>
         <v/>
       </c>
@@ -5852,19 +6017,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Blåbergssjön karta.png", "Blåbergssjön")</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="X42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Blåbergssjön georefererad karta.tif", "Blåbergssjön")</f>
+        <v/>
+      </c>
+      <c r="Z42">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Blåbergssjön FSC-klagomål.docx", "Blåbergssjön")</f>
         <v/>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Blåbergssjön FSC-klagomål mail.docx", "Blåbergssjön")</f>
         <v/>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Blåbergssjön tillsynsbegäran.docx", "Blåbergssjön")</f>
         <v/>
       </c>
-      <c r="AB42">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Blåbergssjön tillsynsbegäran mail.docx", "Blåbergssjön")</f>
         <v/>
       </c>
@@ -5958,22 +6127,26 @@
         <v/>
       </c>
       <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Gåstjärnen georefererad karta.tif", "Gåstjärnen")</f>
+        <v/>
+      </c>
+      <c r="Y43">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/knärot/Gåstjärnen karta knärot.png", "Gåstjärnen")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Z43">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Gåstjärnen FSC-klagomål.docx", "Gåstjärnen")</f>
         <v/>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Gåstjärnen FSC-klagomål mail.docx", "Gåstjärnen")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AB43">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Gåstjärnen tillsynsbegäran.docx", "Gåstjärnen")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AC43">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gåstjärnen tillsynsbegäran mail.docx", "Gåstjärnen")</f>
         <v/>
       </c>
@@ -6065,19 +6238,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Stornäsholmen karta.png", "Stornäsholmen")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Stornäsholmen georefererad karta.tif", "Stornäsholmen")</f>
+        <v/>
+      </c>
+      <c r="Z44">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Stornäsholmen FSC-klagomål.docx", "Stornäsholmen")</f>
         <v/>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Stornäsholmen FSC-klagomål mail.docx", "Stornäsholmen")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Stornäsholmen tillsynsbegäran.docx", "Stornäsholmen")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stornäsholmen tillsynsbegäran mail.docx", "Stornäsholmen")</f>
         <v/>
       </c>
@@ -6164,19 +6341,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Käringberget SO karta.png", "Käringberget SO")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Käringberget SO georefererad karta.tif", "Käringberget SO")</f>
+        <v/>
+      </c>
+      <c r="Z45">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Käringberget SO FSC-klagomål.docx", "Käringberget SO")</f>
         <v/>
       </c>
-      <c r="Z45">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Käringberget SO FSC-klagomål mail.docx", "Käringberget SO")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Käringberget SO tillsynsbegäran.docx", "Käringberget SO")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Käringberget SO tillsynsbegäran mail.docx", "Käringberget SO")</f>
         <v/>
       </c>
@@ -6263,19 +6444,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Tosktjärnberget karta.png", "Tosktjärnberget")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Tosktjärnberget georefererad karta.tif", "Tosktjärnberget")</f>
+        <v/>
+      </c>
+      <c r="Z46">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Tosktjärnberget FSC-klagomål.docx", "Tosktjärnberget")</f>
         <v/>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Tosktjärnberget FSC-klagomål mail.docx", "Tosktjärnberget")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Tosktjärnberget tillsynsbegäran.docx", "Tosktjärnberget")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tosktjärnberget tillsynsbegäran mail.docx", "Tosktjärnberget")</f>
         <v/>
       </c>
@@ -6360,19 +6545,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lill-Smaltjärnen karta.png", "Lill-Smaltjärnen")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lill-Smaltjärnen georefererad karta.tif", "Lill-Smaltjärnen")</f>
+        <v/>
+      </c>
+      <c r="Z47">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lill-Smaltjärnen FSC-klagomål.docx", "Lill-Smaltjärnen")</f>
         <v/>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lill-Smaltjärnen FSC-klagomål mail.docx", "Lill-Smaltjärnen")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lill-Smaltjärnen tillsynsbegäran.docx", "Lill-Smaltjärnen")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lill-Smaltjärnen tillsynsbegäran mail.docx", "Lill-Smaltjärnen")</f>
         <v/>
       </c>
@@ -6456,19 +6645,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Alingsås karta.png", "Alingsås")</f>
         <v/>
       </c>
-      <c r="Y48">
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Alingsås georefererad karta.tif", "Alingsås")</f>
+        <v/>
+      </c>
+      <c r="Z48">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Alingsås FSC-klagomål.docx", "Alingsås")</f>
         <v/>
       </c>
-      <c r="Z48">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Alingsås FSC-klagomål mail.docx", "Alingsås")</f>
         <v/>
       </c>
-      <c r="AA48">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Alingsås tillsynsbegäran.docx", "Alingsås")</f>
         <v/>
       </c>
-      <c r="AB48">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Alingsås tillsynsbegäran mail.docx", "Alingsås")</f>
         <v/>
       </c>
@@ -6552,19 +6745,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Norrnäs karta.png", "Norrnäs")</f>
         <v/>
       </c>
-      <c r="Y49">
+      <c r="X49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Norrnäs georefererad karta.tif", "Norrnäs")</f>
+        <v/>
+      </c>
+      <c r="Z49">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Norrnäs FSC-klagomål.docx", "Norrnäs")</f>
         <v/>
       </c>
-      <c r="Z49">
+      <c r="AA49">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Norrnäs FSC-klagomål mail.docx", "Norrnäs")</f>
         <v/>
       </c>
-      <c r="AA49">
+      <c r="AB49">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Norrnäs tillsynsbegäran.docx", "Norrnäs")</f>
         <v/>
       </c>
-      <c r="AB49">
+      <c r="AC49">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Norrnäs tillsynsbegäran mail.docx", "Norrnäs")</f>
         <v/>
       </c>
@@ -6647,19 +6844,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Vitstensberget V karta.png", "Vitstensberget V")</f>
         <v/>
       </c>
-      <c r="Y50">
+      <c r="X50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Vitstensberget V georefererad karta.tif", "Vitstensberget V")</f>
+        <v/>
+      </c>
+      <c r="Z50">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Vitstensberget V FSC-klagomål.docx", "Vitstensberget V")</f>
         <v/>
       </c>
-      <c r="Z50">
+      <c r="AA50">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Vitstensberget V FSC-klagomål mail.docx", "Vitstensberget V")</f>
         <v/>
       </c>
-      <c r="AA50">
+      <c r="AB50">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Vitstensberget V tillsynsbegäran.docx", "Vitstensberget V")</f>
         <v/>
       </c>
-      <c r="AB50">
+      <c r="AC50">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Vitstensberget V tillsynsbegäran mail.docx", "Vitstensberget V")</f>
         <v/>
       </c>
@@ -6742,23 +6943,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lubbliden karta.png", "Lubbliden")</f>
         <v/>
       </c>
-      <c r="Y51">
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lubbliden georefererad karta.tif", "Lubbliden")</f>
+        <v/>
+      </c>
+      <c r="Z51">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lubbliden FSC-klagomål.docx", "Lubbliden")</f>
         <v/>
       </c>
-      <c r="Z51">
+      <c r="AA51">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lubbliden FSC-klagomål mail.docx", "Lubbliden")</f>
         <v/>
       </c>
-      <c r="AA51">
+      <c r="AB51">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lubbliden tillsynsbegäran.docx", "Lubbliden")</f>
         <v/>
       </c>
-      <c r="AB51">
+      <c r="AC51">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lubbliden tillsynsbegäran mail.docx", "Lubbliden")</f>
         <v/>
       </c>
-      <c r="AC51">
+      <c r="AD51">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lubbliden prioriterade fågelarter.docx", "Lubbliden")</f>
         <v/>
       </c>
@@ -6841,19 +7046,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lögdeälven karta.png", "Lögdeälven")</f>
         <v/>
       </c>
-      <c r="Y52">
+      <c r="X52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lögdeälven georefererad karta.tif", "Lögdeälven")</f>
+        <v/>
+      </c>
+      <c r="Z52">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lögdeälven FSC-klagomål.docx", "Lögdeälven")</f>
         <v/>
       </c>
-      <c r="Z52">
+      <c r="AA52">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lögdeälven FSC-klagomål mail.docx", "Lögdeälven")</f>
         <v/>
       </c>
-      <c r="AA52">
+      <c r="AB52">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lögdeälven tillsynsbegäran.docx", "Lögdeälven")</f>
         <v/>
       </c>
-      <c r="AB52">
+      <c r="AC52">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lögdeälven tillsynsbegäran mail.docx", "Lögdeälven")</f>
         <v/>
       </c>
@@ -6936,19 +7145,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lustigbacken karta.png", "Lustigbacken")</f>
         <v/>
       </c>
-      <c r="Y53">
+      <c r="X53">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lustigbacken georefererad karta.tif", "Lustigbacken")</f>
+        <v/>
+      </c>
+      <c r="Z53">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lustigbacken FSC-klagomål.docx", "Lustigbacken")</f>
         <v/>
       </c>
-      <c r="Z53">
+      <c r="AA53">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lustigbacken FSC-klagomål mail.docx", "Lustigbacken")</f>
         <v/>
       </c>
-      <c r="AA53">
+      <c r="AB53">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lustigbacken tillsynsbegäran.docx", "Lustigbacken")</f>
         <v/>
       </c>
-      <c r="AB53">
+      <c r="AC53">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lustigbacken tillsynsbegäran mail.docx", "Lustigbacken")</f>
         <v/>
       </c>
@@ -7030,19 +7243,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Tomasmyren SO karta.png", "Tomasmyren SO")</f>
         <v/>
       </c>
-      <c r="Y54">
+      <c r="X54">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Tomasmyren SO georefererad karta.tif", "Tomasmyren SO")</f>
+        <v/>
+      </c>
+      <c r="Z54">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Tomasmyren SO FSC-klagomål.docx", "Tomasmyren SO")</f>
         <v/>
       </c>
-      <c r="Z54">
+      <c r="AA54">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Tomasmyren SO FSC-klagomål mail.docx", "Tomasmyren SO")</f>
         <v/>
       </c>
-      <c r="AA54">
+      <c r="AB54">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Tomasmyren SO tillsynsbegäran.docx", "Tomasmyren SO")</f>
         <v/>
       </c>
-      <c r="AB54">
+      <c r="AC54">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tomasmyren SO tillsynsbegäran mail.docx", "Tomasmyren SO")</f>
         <v/>
       </c>
@@ -7124,19 +7341,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor/Lill-Lögdåberget V karta.png", "Lill-Lögdåberget V")</f>
         <v/>
       </c>
-      <c r="Y55">
+      <c r="X55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/kartor_geotiff/Lill-Lögdåberget V georefererad karta.tif", "Lill-Lögdåberget V")</f>
+        <v/>
+      </c>
+      <c r="Z55">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomål/Lill-Lögdåberget V FSC-klagomål.docx", "Lill-Lögdåberget V")</f>
         <v/>
       </c>
-      <c r="Z55">
+      <c r="AA55">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/klagomålsmail/Lill-Lögdåberget V FSC-klagomål mail.docx", "Lill-Lögdåberget V")</f>
         <v/>
       </c>
-      <c r="AA55">
+      <c r="AB55">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsyn/Lill-Lögdåberget V tillsynsbegäran.docx", "Lill-Lögdåberget V")</f>
         <v/>
       </c>
-      <c r="AB55">
+      <c r="AC55">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lill-Lögdåberget V tillsynsbegäran mail.docx", "Lill-Lögdåberget V")</f>
         <v/>
       </c>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD65"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -573,6 +573,51 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Klar</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Prio</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Markägare</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Avvanm</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Lst-områd</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Påverkan</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Skogstyp</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Avsatt</t>
         </is>
       </c>
     </row>
@@ -757,6 +802,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Råtjärnberget prioriterade fågelarter.docx", "Råtjärnberget")</f>
         <v/>
       </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Reka avvanm!!!</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v/>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Svea, SCA</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Varierande</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Tall, blan</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -931,6 +1019,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kravattensliden prioriterade fågelarter.docx", "Kravattensliden")</f>
         <v/>
       </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Vnorrland</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -1097,6 +1226,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Röjdtjärnliden prioriterade fågelarter.docx", "Röjdtjärnliden")</f>
         <v/>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Fint,  avvanm</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -1260,6 +1432,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lillgoberget prioriterade fågelarter.docx", "Lillgoberget")</f>
         <v/>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Tips. Bra!</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -1419,6 +1634,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Baksjökullen prioriterade fågelarter.docx", "Baksjökullen")</f>
         <v/>
       </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Ser halvbra ut, stora avvanm</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Hög?</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1575,6 +1833,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Fulberget prioriterade fågelarter.docx", "Fulberget")</f>
         <v/>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Helt ok! Gran och enstaka asp</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1725,6 +2026,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Arnträskbergen prioriterade fågelarter.docx", "Arnträskbergen")</f>
         <v/>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>STORT.  Fokus södra Holmendelarna??</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Svea, Holm</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1874,6 +2218,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Sundsjölandet prioriterade fågelarter.docx", "Sundsjölandet")</f>
         <v/>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Ej rekad</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -2019,6 +2406,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Rislidtjärnarna prioriterade fågelarter.docx", "Rislidtjärnarna")</f>
         <v/>
       </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Sve+Hol+SC</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -2163,6 +2591,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lill-Lögdåberget O prioriterade fågelarter.docx", "Lill-Lögdåberget O")</f>
         <v/>
       </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Fokus avvanm</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -2306,6 +2777,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Tällvattsåsen prioriterade fågelarter.docx", "Tällvattsåsen")</f>
         <v/>
       </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Rekad.  Helt ok, inte mer.</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -2444,6 +2958,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lappberget prioriterade fågelarter.docx", "Lappberget")</f>
         <v/>
       </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Isacs område</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Holmen/SCA</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Tall, gran</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -2581,6 +3138,45 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tyfallsjön tillsynsbegäran mail.docx", "Tyfallsjön")</f>
         <v/>
       </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -2717,6 +3313,45 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Oxliden prioriterade fågelarter.docx", "Oxliden")</f>
         <v/>
       </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -2853,6 +3488,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Gålgoberget prioriterade fågelarter.docx", "Gålgoberget")</f>
         <v/>
       </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -2988,6 +3664,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Orratjärnskullen prioriterade fågelarter.docx", "Orratjärnskullen")</f>
         <v/>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Helt ok</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v/>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Helt</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -3123,6 +3842,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Hötjärnberget prioriterade fågelarter.docx", "Hötjärnberget")</f>
         <v/>
       </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Inv lst 2015. Rekad,  helt OK, V3 i NV</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v/>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -3253,6 +4015,45 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Glesskallberget prioriterade fågelarter.docx", "Glesskallberget")</f>
         <v/>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Stort och bra!?</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v/>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL19" t="n">
+        <v/>
+      </c>
+      <c r="AM19" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -3386,6 +4187,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Stormyrbäcken prioriterade fågelarter.docx", "Stormyrbäcken")</f>
         <v/>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Lämpligt som introobjekt</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v/>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -3517,6 +4361,51 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Bastuberget prioriterade fågelarter.docx", "Bastuberget")</f>
         <v/>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Ser riktigt bra ut!!!</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -3644,6 +4533,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lögdeälven käringberget prioriterade fågelarter.docx", "Lögdeälven käringberget")</f>
         <v/>
       </c>
+      <c r="AE22" t="n">
+        <v/>
+      </c>
+      <c r="AF22" t="n">
+        <v/>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Svea</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -3766,6 +4696,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gåsselmyran tillsynsbegäran mail.docx", "Gåsselmyran")</f>
         <v/>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Helt ok</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v/>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>SCA + Svea</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -3892,6 +4865,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Käringberget SV prioriterade fågelarter.docx", "Käringberget SV")</f>
         <v/>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Avverkad centralt</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v/>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -4017,6 +5033,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Vitstensberget prioriterade fågelarter.docx", "Vitstensberget")</f>
         <v/>
       </c>
+      <c r="AE25" t="n">
+        <v/>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Hela</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -4146,6 +5205,51 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Karlstjärnberget prioriterade fågelarter.docx", "Karlstjärnberget")</f>
         <v/>
       </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>70% avverkat</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Oklart</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -4274,6 +5378,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Herrbergsliden norr prioriterade fågelarter.docx", "Herrbergsliden norr")</f>
         <v/>
       </c>
+      <c r="AE27" t="n">
+        <v/>
+      </c>
+      <c r="AF27" t="n">
+        <v/>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -4401,6 +5546,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget SV prioriterade fågelarter.docx", "Björnberget SV")</f>
         <v/>
       </c>
+      <c r="AE28" t="n">
+        <v/>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Ser bra ut</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -4524,6 +5712,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Björnberget NV prioriterade fågelarter.docx", "Björnberget NV")</f>
         <v/>
       </c>
+      <c r="AE29" t="n">
+        <v/>
+      </c>
+      <c r="AF29" t="n">
+        <v/>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -4646,6 +5875,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kläpptjärnen prioriterade fågelarter.docx", "Kläpptjärnen")</f>
         <v/>
       </c>
+      <c r="AE30" t="n">
+        <v/>
+      </c>
+      <c r="AF30" t="n">
+        <v/>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -4771,6 +6041,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Johannesbomyran prioriterade fågelarter.docx", "Johannesbomyran")</f>
         <v/>
       </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Rekad.  Halvbra. Avverkad.</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v/>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
@@ -4891,6 +6204,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Stockbäcken prioriterade fågelarter.docx", "Stockbäcken")</f>
         <v/>
       </c>
+      <c r="AE32" t="n">
+        <v/>
+      </c>
+      <c r="AF32" t="n">
+        <v/>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -5014,6 +6368,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lögdaselet prioriterade fågelarter.docx", "Lögdaselet")</f>
         <v/>
       </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>REKA avv-anm</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v/>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -5133,6 +6530,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Holmtjärnen prioriterade fågelarter.docx", "Holmtjärnen")</f>
         <v/>
       </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Troligen rekad. Inte så bra.</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v/>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
@@ -5252,6 +6692,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Aspmyrbäcken prioriterade fågelarter.docx", "Aspmyrbäcken")</f>
         <v/>
       </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Fokus S delarna</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v/>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Svea</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -5369,6 +6852,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Gubbmyran prioriterade fågelarter.docx", "Gubbmyran")</f>
         <v/>
       </c>
+      <c r="AE36" t="n">
+        <v/>
+      </c>
+      <c r="AF36" t="n">
+        <v/>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -5488,6 +7012,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Kälkåsen prioriterade fågelarter.docx", "Kälkåsen")</f>
         <v/>
       </c>
+      <c r="AE37" t="n">
+        <v/>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -5599,6 +7166,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Björnberget N tillsynsbegäran mail.docx", "Björnberget N")</f>
         <v/>
       </c>
+      <c r="AE38" t="n">
+        <v/>
+      </c>
+      <c r="AF38" t="n">
+        <v/>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -5710,6 +7318,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Trollberget tillsynsbegäran mail.docx", "Trollberget")</f>
         <v/>
       </c>
+      <c r="AE39" t="n">
+        <v/>
+      </c>
+      <c r="AF39" t="n">
+        <v/>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -5819,6 +7468,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stensjöåsen tillsynsbegäran mail.docx", "Stensjöåsen")</f>
         <v/>
       </c>
+      <c r="AE40" t="n">
+        <v/>
+      </c>
+      <c r="AF40" t="n">
+        <v/>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -5928,6 +7618,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stor-Svartliden tillsynsbegäran mail.docx", "Stor-Svartliden")</f>
         <v/>
       </c>
+      <c r="AE41" t="n">
+        <v/>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Holmen+Sve</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -6037,6 +7770,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Blåbergssjön tillsynsbegäran mail.docx", "Blåbergssjön")</f>
         <v/>
       </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Rekad.  Artrik tallskog.</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
+        <v/>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
@@ -6150,6 +7926,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Gåstjärnen tillsynsbegäran mail.docx", "Gåstjärnen")</f>
         <v/>
       </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Högst halvbra</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v/>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -6258,6 +8077,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Stornäsholmen tillsynsbegäran mail.docx", "Stornäsholmen")</f>
         <v/>
       </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>ej rekad</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
+        <v/>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -6361,6 +8223,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Käringberget SO tillsynsbegäran mail.docx", "Käringberget SO")</f>
         <v/>
       </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>delvis avsatt</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
+        <v/>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Svea</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -6464,6 +8369,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tosktjärnberget tillsynsbegäran mail.docx", "Tosktjärnberget")</f>
         <v/>
       </c>
+      <c r="AE46" t="n">
+        <v/>
+      </c>
+      <c r="AF46" t="n">
+        <v/>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Hård</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -6565,6 +8511,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lill-Smaltjärnen tillsynsbegäran mail.docx", "Lill-Smaltjärnen")</f>
         <v/>
       </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Hårt hugget.</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
+        <v/>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -6665,6 +8654,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Alingsås tillsynsbegäran mail.docx", "Alingsås")</f>
         <v/>
       </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Ratat av LST i SNUS,  faktiskt ganska bra nu enligt Carl</t>
+        </is>
+      </c>
+      <c r="AF48" t="n">
+        <v/>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Svea</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -6765,6 +8797,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Norrnäs tillsynsbegäran mail.docx", "Norrnäs")</f>
         <v/>
       </c>
+      <c r="AE49" t="n">
+        <v/>
+      </c>
+      <c r="AF49" t="n">
+        <v/>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
@@ -6864,6 +8937,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Vitstensberget V tillsynsbegäran mail.docx", "Vitstensberget V")</f>
         <v/>
       </c>
+      <c r="AE50" t="n">
+        <v/>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Helt</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
@@ -6967,6 +9083,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/fåglar/Lubbliden prioriterade fågelarter.docx", "Lubbliden")</f>
         <v/>
       </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Ganska hårt hugget, men rikt på lunglav och hänglav.  kan finnas finare delar.</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
+        <v/>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Svea</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -7066,6 +9225,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lögdeälven tillsynsbegäran mail.docx", "Lögdeälven")</f>
         <v/>
       </c>
+      <c r="AE52" t="n">
+        <v/>
+      </c>
+      <c r="AF52" t="n">
+        <v/>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Svea</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Ekopark</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -7165,6 +9365,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lustigbacken tillsynsbegäran mail.docx", "Lustigbacken")</f>
         <v/>
       </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>ej rekad</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v/>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -7263,6 +9506,47 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Tomasmyren SO tillsynsbegäran mail.docx", "Tomasmyren SO")</f>
         <v/>
       </c>
+      <c r="AE54" t="n">
+        <v/>
+      </c>
+      <c r="AF54" t="n">
+        <v/>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -7361,6 +9645,49 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2025_BJURHOLM/tillsynsmail/Lill-Lögdåberget V tillsynsbegäran mail.docx", "Lill-Lögdåberget V")</f>
         <v/>
       </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Kan vara bra!</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
+        <v/>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Dikning</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Lövrik gra</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
@@ -7427,6 +9754,49 @@
         <v>0</v>
       </c>
       <c r="U56" s="2" t="inlineStr"/>
+      <c r="AE56" t="n">
+        <v/>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -7493,6 +9863,49 @@
         <v>0</v>
       </c>
       <c r="U57" s="2" t="inlineStr"/>
+      <c r="AE57" t="n">
+        <v/>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
@@ -7559,6 +9972,47 @@
         <v>0</v>
       </c>
       <c r="U58" s="2" t="inlineStr"/>
+      <c r="AE58" t="n">
+        <v/>
+      </c>
+      <c r="AF58" t="n">
+        <v/>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Hård</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -7625,6 +10079,47 @@
         <v>0</v>
       </c>
       <c r="U59" s="2" t="inlineStr"/>
+      <c r="AE59" t="n">
+        <v/>
+      </c>
+      <c r="AF59" t="n">
+        <v/>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -7691,6 +10186,49 @@
         <v>0</v>
       </c>
       <c r="U60" s="2" t="inlineStr"/>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Hyggesbränt i SO</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
+        <v/>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
@@ -7757,6 +10295,47 @@
         <v>0</v>
       </c>
       <c r="U61" s="2" t="inlineStr"/>
+      <c r="AE61" t="n">
+        <v/>
+      </c>
+      <c r="AF61" t="n">
+        <v/>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>nej</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
@@ -7823,6 +10402,49 @@
         <v>0</v>
       </c>
       <c r="U62" s="2" t="inlineStr"/>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Ej rekad</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
+        <v/>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Medel</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
@@ -7889,6 +10511,49 @@
         <v>0</v>
       </c>
       <c r="U63" s="2" t="inlineStr"/>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Ej rekad</t>
+        </is>
+      </c>
+      <c r="AF63" t="n">
+        <v/>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Rel låg</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
@@ -7955,6 +10620,49 @@
         <v>0</v>
       </c>
       <c r="U64" s="2" t="inlineStr"/>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Ej rekad</t>
+        </is>
+      </c>
+      <c r="AF64" t="n">
+        <v/>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8021,6 +10729,47 @@
         <v>0</v>
       </c>
       <c r="U65" s="2" t="inlineStr"/>
+      <c r="AE65" t="n">
+        <v/>
+      </c>
+      <c r="AF65" t="n">
+        <v/>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Hård/låg</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Bland</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -7522,10 +7522,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -8710,10 +8710,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -9421,10 +9421,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -9810,10 +9810,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -10349,10 +10349,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -10458,10 +10458,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -10567,10 +10567,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
